--- a/archive/2026-10-24/svod.xlsx
+++ b/archive/2026-10-24/svod.xlsx
@@ -150,12 +150,12 @@
     <t xml:space="preserve">ПСО</t>
   </si>
   <si>
+    <t xml:space="preserve">Гараж-2</t>
+  </si>
+  <si>
     <t xml:space="preserve">СБ</t>
   </si>
   <si>
-    <t xml:space="preserve">Гараж-2</t>
-  </si>
-  <si>
     <t xml:space="preserve">ДРиСУ УТТ</t>
   </si>
   <si>
@@ -1911,6 +1911,15 @@
     <t xml:space="preserve">20-176AG12</t>
   </si>
   <si>
+    <t xml:space="preserve">C17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РМУ гараж 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-Н348212</t>
+  </si>
+  <si>
     <t xml:space="preserve">D17</t>
   </si>
   <si>
@@ -1948,15 +1957,6 @@
   </si>
   <si>
     <t xml:space="preserve">20-Н341312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">РМУ гараж 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-Н348212</t>
   </si>
   <si>
     <t xml:space="preserve">ДРиСУ</t>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="AL14" s="9" t="n">
         <f aca="false">SUMIFS('Исходные данные'!$I$2:$I$955,'Исходные данные'!$D$2:$D$955,AL$1,'Исходные данные'!$F$2:$F$955,$A14)</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AM14" s="9" t="n">
         <f aca="false">SUMIFS('Исходные данные'!$J$2:$J$955,'Исходные данные'!$D$2:$D$955,AL$1,'Исходные данные'!$F$2:$F$955,$A14)</f>
@@ -9482,15 +9482,15 @@
       </c>
       <c r="BY14" s="9" t="n">
         <f aca="false">SUMIFS('Исходные данные'!$J$2:$J$955,'Исходные данные'!$D$2:$D$955,BX$1,'Исходные данные'!$F$2:$F$955,$A14)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BZ14" s="9" t="n">
         <f aca="false">SUMIFS('Исходные данные'!$I$2:$I$955,'Исходные данные'!$D$2:$D$955,BZ$1,'Исходные данные'!$F$2:$F$955,$A14)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CA14" s="9" t="n">
         <f aca="false">SUMIFS('Исходные данные'!$J$2:$J$955,'Исходные данные'!$D$2:$D$955,BZ$1,'Исходные данные'!$F$2:$F$955,$A14)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB14" s="9" t="n">
         <f aca="false">SUMIFS('Исходные данные'!$I$2:$I$955,'Исходные данные'!$D$2:$D$955,CB$1,'Исходные данные'!$F$2:$F$955,$A14)</f>
@@ -12038,11 +12038,11 @@
       </c>
       <c r="AL22" s="9" t="n">
         <f aca="false">SUMIFS('Исходные данные'!$I$2:$I$955,'Исходные данные'!$D$2:$D$955,AL$1,'Исходные данные'!$F$2:$F$955,$A22)</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AM22" s="9" t="n">
         <f aca="false">SUMIFS('Исходные данные'!$J$2:$J$955,'Исходные данные'!$D$2:$D$955,AL$1,'Исходные данные'!$F$2:$F$955,$A22)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN22" s="9" t="n">
         <f aca="false">SUMIFS('Исходные данные'!$I$2:$I$955,'Исходные данные'!$D$2:$D$955,AN$1,'Исходные данные'!$F$2:$F$955,$A22)</f>
@@ -12190,15 +12190,15 @@
       </c>
       <c r="BX22" s="9" t="n">
         <f aca="false">SUMIFS('Исходные данные'!$I$2:$I$955,'Исходные данные'!$D$2:$D$955,BX$1,'Исходные данные'!$F$2:$F$955,$A22)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BY22" s="9" t="n">
         <f aca="false">SUMIFS('Исходные данные'!$J$2:$J$955,'Исходные данные'!$D$2:$D$955,BX$1,'Исходные данные'!$F$2:$F$955,$A22)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ22" s="9" t="n">
         <f aca="false">SUMIFS('Исходные данные'!$I$2:$I$955,'Исходные данные'!$D$2:$D$955,BZ$1,'Исходные данные'!$F$2:$F$955,$A22)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CA22" s="9" t="n">
         <f aca="false">SUMIFS('Исходные данные'!$J$2:$J$955,'Исходные данные'!$D$2:$D$955,BZ$1,'Исходные данные'!$F$2:$F$955,$A22)</f>
@@ -23563,11 +23563,11 @@
       </c>
       <c r="AL56" s="10" t="n">
         <f aca="false">SUM(AL3:AL55)</f>
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AM56" s="10" t="n">
         <f aca="false">SUM(AM3:AM55)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN56" s="10" t="n">
         <f aca="false">SUM(AN3:AN55)</f>
@@ -23715,7 +23715,7 @@
       </c>
       <c r="BX56" s="10" t="n">
         <f aca="false">SUM(BX3:BX55)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BY56" s="10" t="n">
         <f aca="false">SUM(BY3:BY55)</f>
@@ -23723,11 +23723,11 @@
       </c>
       <c r="BZ56" s="10" t="n">
         <f aca="false">SUM(BZ3:BZ55)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CA56" s="10" t="n">
         <f aca="false">SUM(CA3:CA55)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB56" s="10" t="n">
         <f aca="false">SUM(CB3:CB55)</f>
@@ -23844,7 +23844,7 @@
       <c r="AK57" s="11"/>
       <c r="AL57" s="11" t="n">
         <f aca="false">AL56+AM56</f>
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AM57" s="11"/>
       <c r="AN57" s="11" t="n">
@@ -23939,12 +23939,12 @@
       <c r="BW57" s="11"/>
       <c r="BX57" s="11" t="n">
         <f aca="false">BX56+BY56</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BY57" s="11"/>
       <c r="BZ57" s="11" t="n">
         <f aca="false">BZ56+CA56</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="CA57" s="11"/>
       <c r="CB57" s="11" t="n">
@@ -35401,16 +35401,16 @@
         <v>629</v>
       </c>
       <c r="D198" s="114" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="E198" s="114" t="s">
         <v>630</v>
       </c>
       <c r="F198" s="115" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="G198" s="114" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="H198" s="114" t="s">
         <v>383</v>
@@ -35434,13 +35434,13 @@
         <v>622</v>
       </c>
       <c r="C199" s="114" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="D199" s="114" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="E199" s="114" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F199" s="115" t="s">
         <v>70</v>
@@ -35464,19 +35464,19 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="114" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B200" s="114" t="s">
         <v>622</v>
       </c>
       <c r="C200" s="114" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="D200" s="114" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="E200" s="114" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F200" s="115" t="s">
         <v>70</v>
@@ -35500,34 +35500,34 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="114" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B201" s="114" t="s">
         <v>622</v>
       </c>
       <c r="C201" s="114" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="D201" s="114" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="E201" s="114" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F201" s="115" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="G201" s="114" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="H201" s="114" t="s">
         <v>383</v>
       </c>
       <c r="I201" s="116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J201" s="116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K201" s="114"/>
       <c r="L201" s="114" t="s">
@@ -35536,19 +35536,19 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="114" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B202" s="114" t="s">
         <v>622</v>
       </c>
       <c r="C202" s="114" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="D202" s="114" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="E202" s="114" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F202" s="115" t="s">
         <v>86</v>
@@ -35560,10 +35560,10 @@
         <v>383</v>
       </c>
       <c r="I202" s="116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J202" s="116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K202" s="114"/>
       <c r="L202" s="114" t="s">
@@ -35572,19 +35572,19 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="114" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B203" s="114" t="s">
         <v>622</v>
       </c>
       <c r="C203" s="114" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="D203" s="114" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="E203" s="114" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F203" s="115" t="s">
         <v>86</v>
@@ -35608,16 +35608,16 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="114" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B204" s="114" t="s">
         <v>622</v>
       </c>
       <c r="C204" s="114" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
       <c r="D204" s="114" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E204" s="114" t="s">
         <v>643</v>
@@ -36226,10 +36226,10 @@
         <v>622</v>
       </c>
       <c r="C221" s="114" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D221" s="114" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E221" s="114" t="s">
         <v>670</v>
@@ -36262,10 +36262,10 @@
         <v>622</v>
       </c>
       <c r="C222" s="114" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D222" s="114" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E222" s="114" t="s">
         <v>671</v>
@@ -45274,7 +45274,7 @@
     </row>
     <row r="485" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="114" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B485" s="114" t="s">
         <v>1065</v>
@@ -45376,7 +45376,7 @@
     </row>
     <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A488" s="114" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
       <c r="B488" s="114" t="s">
         <v>1065</v>
@@ -45416,10 +45416,10 @@
         <v>1065</v>
       </c>
       <c r="C489" s="114" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D489" s="114" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E489" s="114" t="s">
         <v>1117</v>
@@ -45450,10 +45450,10 @@
         <v>1065</v>
       </c>
       <c r="C490" s="114" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D490" s="114" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E490" s="114" t="s">
         <v>1118</v>
@@ -46806,7 +46806,7 @@
     </row>
     <row r="530" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A530" s="114" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="B530" s="114" t="s">
         <v>1065</v>
@@ -46840,7 +46840,7 @@
     </row>
     <row r="531" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A531" s="114" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="B531" s="114" t="s">
         <v>1065</v>
